--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -601,7 +601,7 @@
         <v>45763</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45737</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>45118</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>45775</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46037</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45826</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>46213</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45932</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45666</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46071</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45826</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46201</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>45919</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45911</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45967</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46246</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>46248</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45590</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45959</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45625</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>46147</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>46230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45992</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>45217</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45792</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>46281</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>46177</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>45848</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>46205</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>46281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45653</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>46013</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>45833</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45533</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45003</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45925</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45895</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45981</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>45902</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>46244</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>46112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45264</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>46036</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>46006</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45841</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>46089</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46178</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>46198</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>46248</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>45525</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>45623</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>46112</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>46078</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>44725</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45982</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>46248</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44637</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>46008</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45833</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>45985</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>46105</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>46002</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44796</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45890</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>46085</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45848</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>46202</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>46202</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>45481</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>46248</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>46248</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>46206</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45418</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>46237</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>45835</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45782</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44545</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45791</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45966</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45967</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>45320</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44881</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45699</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44742</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>45533</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45219</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45159</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45756</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>46162</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>46198</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45180</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45007</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45090</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45775</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45852</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>44589</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44470</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44893</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44529</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44897</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45077</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>46006</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45533</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>46029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45098</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>45576</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45540</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44953</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45618</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>46276</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>46237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44959</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45471</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>45826</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45264</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45377</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>46089</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>44553</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44546</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>44813</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44515</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>44832</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>44838</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>44459</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>44601</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>44705</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44516</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>44747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>44848</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>44673</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>44788</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44489</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44609</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>44578</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>44546</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>44530</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44466</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>44488</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44480</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44749</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>44589</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44543</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>44680</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44489</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44858</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>44796</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>44810</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44522</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>44613</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>44656</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44726</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45351</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45351</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45692</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>44874</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45756</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>45590</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>45637</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44630</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45572</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45642</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45264</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45167</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45743</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45530</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45568</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45622</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44531</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45757</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45602</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>44768</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>44852</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44896</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44810</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45695</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>44859</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45184</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45280</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45412</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45749</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45240</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44959</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>44482</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44898</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>44995</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45090</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45194</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45253</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45159</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44831</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45132</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45104</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45645</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44484</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45232</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45019</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45090</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45279</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45433</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45453</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>44617</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45232</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44903</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45463</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45420</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45259</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>45646</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>44518</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45611</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45259</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>44942</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>44755</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45667</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>45299</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45775</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45615</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45617</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45820</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>44907</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>44781</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45531</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45387</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45985</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45624</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>44517</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45544</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44845</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>44658</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45477</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45077</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45260</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46048</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45252</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>46119</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>45891</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45891</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45812</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45252</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44847</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45800</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>44830</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45894</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45894</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45896</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45897</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45799</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>44956</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45404</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45898</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45901</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45562</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>44900</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>44581</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>45902</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44911</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45902</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45904</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>46141</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>46141</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45296</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>45385</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>46140</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>46141</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>46141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>46141</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>46141</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45911</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45505</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45576</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45912</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44497</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45916</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>46048</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45502</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44909</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>44644</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45917</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45919</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45188</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>44865</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45748</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>45198</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45924</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45925</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45761</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45775</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>45929</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45929</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>45190</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>46142</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>46142</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>46142</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45551</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45930</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>45931</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44897</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>46142</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45497</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>44600</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>46147</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>46147</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>46141</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45931</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>45931</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>46146</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45937</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45937</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45938</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46139</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>45474</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>45938</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45551</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>45460</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>46051</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>46148</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44725</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>46148</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>44837</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45615</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>46148</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>46148</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>45771</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>45761</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>46153</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45502</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45296</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45958</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45958</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45299</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45147</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44859</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45771</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45259</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45961</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>45960</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>45960</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>45229</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45960</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>45001</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45960</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45960</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45960</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>45965</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45965</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45063</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>45966</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45254</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>45967</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45188</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45572</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45967</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>46155</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>44900</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>46101</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45968</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45769</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45337</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45977</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45979</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>45979</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45196</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45981</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>46155</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45982</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45203</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>45524</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>46161</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45968</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>44804</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45988</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>46160</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45992</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45992</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>45992</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>46161</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46160</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>45222</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45404</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>46160</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>46163</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45145</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>46162</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>46163</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45593</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45205</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>45999</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>45239</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>45278</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45463</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45574</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>44915</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46001</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>44482</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45210</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45153</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>46001</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>44515</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>46164</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>46002</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>46002</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>46002</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>46003</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>46006</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45632</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>46006</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>46007</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>46009</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>46009</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>46008</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>46008</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>45756</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45057</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>46008</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>46094</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45807</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45807</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>46013</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>45036</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45188</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>44581</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>45628</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>46168</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45954</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>46013</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>45196</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>46014</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>46014</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45775</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38558,7 +38558,7 @@
         <v>45981</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>46168</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>46170</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>46170</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>46024</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44699</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46170</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46174</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45162</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45279</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46029</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46041</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>44945</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>46042</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45184</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>46043</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>46044</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44957</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>44957</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45203</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45999</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45105</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45425</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>46098</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>46057</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>46056</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45147</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>45253</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>46163</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>46057</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44887</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45911</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46059</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>46063</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>46064</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46065</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>46182</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>45173</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45691</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>46066</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45573</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>46072</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>46148</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>46076</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>45761</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>46184</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45247</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>46080</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>46184</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>46084</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45567</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45415</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>45210</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45105</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>46085</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>46188</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>46085</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45499</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>46090</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45420</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45554</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>46185</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45174</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>46190</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>46091</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>46091</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>44838</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>46052</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
         <v>46190</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>46098</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45695</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>46191</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43884,7 +43884,7 @@
         <v>46191</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>46191</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>46191</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>46191</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>46191</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>46191</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>46191</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44420,7 +44420,7 @@
         <v>46195</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>46196</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>45334</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>46105</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>46197</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>44838</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>46197</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44642</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45014,7 +45014,7 @@
         <v>46197</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45756</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>46112</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>45524</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>46244</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>45544</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>46201</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45343</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45072</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>46119</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>46119</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>46119</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45910,7 +45910,7 @@
         <v>46121</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>46122</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45754</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>46245</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>46126</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>46202</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>46202</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>46127</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>46202</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46567,7 +46567,7 @@
         <v>45215</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>46127</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45476</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45476</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>46245</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>46246</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>46246</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>46134</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>45460</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>44957</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>46135</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45567</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45363</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>46106</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47589,7 +47589,7 @@
         <v>46133</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>46105</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45834</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45440</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45632</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>45810</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>45981</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>46062</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45576</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45632</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>45628</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>44953</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>44953</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45631</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>46205</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>46205</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48767,7 +48767,7 @@
         <v>46248</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>44819</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45272</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>46248</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49064,7 +49064,7 @@
         <v>45376</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49137,7 +49137,7 @@
         <v>44937</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44806</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>44533</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45279</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>45229</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45615</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49575,7 +49575,7 @@
         <v>45008</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49648,7 +49648,7 @@
         <v>45761</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>45761</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>44589</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45194</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>45756</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>46211</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>45162</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>45259</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>45756</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>46258</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45188</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>45448</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50544,7 +50544,7 @@
         <v>44694</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>46260</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50690,7 +50690,7 @@
         <v>44851</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45334</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45520</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50914,7 +50914,7 @@
         <v>46260</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45520</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45561</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>46260</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         <v>46220</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45572</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51352,7 +51352,7 @@
         <v>45607</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45567</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51498,7 +51498,7 @@
         <v>45410</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>46266</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51644,7 +51644,7 @@
         <v>45264</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>45264</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51800,7 +51800,7 @@
         <v>46266</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51873,7 +51873,7 @@
         <v>45551</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>46268</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45408</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52092,7 +52092,7 @@
         <v>46266</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>45784</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>46274</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52311,7 +52311,7 @@
         <v>46233</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>46276</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52462,7 +52462,7 @@
         <v>46279</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45625</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45625</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52681,7 +52681,7 @@
         <v>45785</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>46237</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45638</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>46237</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45725</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53046,7 +53046,7 @@
         <v>45625</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>44720</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45232</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>45791</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53338,7 +53338,7 @@
         <v>45272</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>46239</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45797</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>45715</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53630,7 +53630,7 @@
         <v>44796</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45049</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         <v>46282</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
         <v>45798</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53932,7 +53932,7 @@
         <v>46282</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45798</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54088,7 +54088,7 @@
         <v>44473</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>46282</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45807</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45497</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54385,7 +54385,7 @@
         <v>45810</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45439</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45625</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54604,7 +54604,7 @@
         <v>45810</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54677,7 +54677,7 @@
         <v>45705</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45810</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45813</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>45812</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45742</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55047,7 +55047,7 @@
         <v>45821</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>45820</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55198,7 +55198,7 @@
         <v>45820</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>45820</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45825</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55422,7 +55422,7 @@
         <v>45826</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55495,7 +55495,7 @@
         <v>45826</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55568,7 +55568,7 @@
         <v>45831</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55641,7 +55641,7 @@
         <v>45831</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>45831</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55787,7 +55787,7 @@
         <v>45831</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55860,7 +55860,7 @@
         <v>45846</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45855</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56006,7 +56006,7 @@
         <v>45358</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>45866</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56152,7 +56152,7 @@
         <v>45874</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>45072</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56298,7 +56298,7 @@
         <v>45876</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>45881</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56444,7 +56444,7 @@
         <v>45614</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45755</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56595,7 +56595,7 @@
         <v>45645</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56668,7 +56668,7 @@
         <v>45728</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>45341</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56819,7 +56819,7 @@
         <v>45315</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>44893</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>44522</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>44550</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45258</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>44602</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57282,7 +57282,7 @@
         <v>45616</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57360,7 +57360,7 @@
         <v>45881</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>45915</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57516,7 +57516,7 @@
         <v>45679</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>46021</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57662,7 +57662,7 @@
         <v>46035</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>46035</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57818,7 +57818,7 @@
         <v>46043</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57896,7 +57896,7 @@
         <v>46125</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -601,7 +601,7 @@
         <v>45763</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45118</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45737</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>45775</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46037</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45826</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>46213</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45932</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45666</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46071</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45826</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46201</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>45967</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45911</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>46246</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46248</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>46287</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45959</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45590</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45625</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>46230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>45992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45217</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45792</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46281</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46177</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46205</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>46281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45848</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45833</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45653</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45533</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>45003</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45925</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>45895</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45981</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45902</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46244</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>46112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>46036</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45264</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>46006</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45841</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46089</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>46178</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>46276</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>45623</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>46112</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>46078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>44725</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45982</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>46248</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44637</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>46105</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>46008</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45985</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>45833</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>45418</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45890</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>46085</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45481</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>45835</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45848</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>46202</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>46202</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>46206</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>46276</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>46237</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>46248</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>46248</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45782</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44545</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45967</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>45966</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45791</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>46008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45320</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44881</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45699</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>44742</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45775</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45007</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>45090</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>46162</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>45852</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45159</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45180</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>46198</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45756</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45219</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45533</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>44589</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44470</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>45533</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>46029</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>44893</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>44959</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44897</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>45471</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>46006</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45826</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>44529</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>46237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45618</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45576</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44953</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45098</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45077</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45540</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45264</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>45377</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>46089</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44553</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44546</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>44813</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44515</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44832</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>44838</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44601</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44705</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44516</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>44747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44848</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44673</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44788</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44489</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44609</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>44578</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44546</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44530</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>44466</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44488</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>44480</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44749</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44589</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>44543</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>44680</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>44489</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>44858</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44796</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44810</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>44522</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>44656</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>44613</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>44726</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45334</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45412</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45222</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44847</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45460</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45253</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45420</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45210</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45425</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45415</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44497</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>44720</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44796</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>46014</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46013</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45715</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45954</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>46013</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44852</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>46024</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45524</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45272</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45049</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45791</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44874</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45174</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45798</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45755</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45797</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>45798</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>44531</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44482</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>44473</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44819</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>46029</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45894</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45891</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45800</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45894</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>46041</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45499</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45896</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45799</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>44898</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>46042</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45897</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>46044</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>44911</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>45898</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>46043</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>44581</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45460</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45901</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44956</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45567</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45902</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>45904</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45646</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45911</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>46056</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>46057</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45912</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>46057</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45911</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>46059</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45916</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45617</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45667</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45551</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45917</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44945</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>46063</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46064</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45919</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>46065</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>46066</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>46072</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45925</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44942</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>46076</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45240</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>45929</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>45930</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>45929</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>46080</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45810</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45625</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45497</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45439</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45931</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>46084</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>46085</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>46085</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45931</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44995</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45404</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>45573</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>45931</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45576</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46091</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45810</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45938</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44694</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45937</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>46090</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>46091</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45691</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>45229</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>45938</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44907</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45937</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44897</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45554</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45203</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45057</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45574</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>46052</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45810</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>46098</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45184</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45615</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45952</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45279</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>46112</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45742</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45958</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45958</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45960</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45960</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45960</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45960</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45960</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45960</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>46121</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>46119</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>46119</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>44831</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>46119</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45961</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>46122</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45965</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45019</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45965</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46127</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45090</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>46127</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45968</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45705</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45967</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45812</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45967</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45966</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>45813</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45602</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>46126</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45145</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45631</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45474</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45977</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45979</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45980</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45979</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>46133</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45982</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45981</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>46105</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>46134</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>46106</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>44642</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45645</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>45820</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45632</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>45624</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>46119</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45988</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45184</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44768</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>46135</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45992</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45992</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45812</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>45968</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45992</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>45756</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>44658</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>45810</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44810</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44517</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>45385</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>46062</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>45999</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44845</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45239</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45278</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45593</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45463</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45205</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>46001</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>46001</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>44959</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>46002</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>46002</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>46002</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45981</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46006</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>46003</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>46006</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45820</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>46008</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>44482</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>46008</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>45188</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>46007</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45530</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46008</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45628</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>45820</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>45820</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>46009</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45807</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45562</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>45807</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>45544</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>46009</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46014</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45502</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45260</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45252</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45572</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>45821</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>46140</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>46048</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45063</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45826</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>45826</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44851</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>44533</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45985</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>46048</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45173</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45825</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>44518</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45834</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45775</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>46141</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>46142</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>46142</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46141</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45524</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>46141</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45476</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45476</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>46141</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45576</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>44484</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>46142</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45077</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>46141</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>46141</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>45334</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>46139</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>46051</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>46141</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>46146</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45831</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>46148</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>46148</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45232</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>46148</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>44806</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>46148</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>45264</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45264</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>44837</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46147</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>46147</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>45252</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45632</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45831</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45831</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45831</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>45253</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>46101</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45147</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45254</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45299</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45280</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>45757</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46153</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>44903</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45105</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>46155</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45296</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45520</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>46160</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>46160</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>46160</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>44915</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>45259</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>45761</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>46161</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45463</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45264</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>44896</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>46162</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>46161</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>46163</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>46164</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45846</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>45756</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>46163</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>45981</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>46094</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>46168</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45343</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46168</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45387</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>45855</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>45561</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>45259</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>45132</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>46170</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>46170</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45358</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45105</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>44600</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>45279</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>46170</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45159</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45505</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>45866</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>46174</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>45544</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44957</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>45104</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42902,7 +42902,7 @@
         <v>46163</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45999</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>45567</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>44589</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45692</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45771</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>46098</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45761</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>46182</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>46148</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>45410</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45611</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>46184</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>46185</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43939,7 +43939,7 @@
         <v>46188</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45072</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>46191</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>45874</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>46191</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44309,7 +44309,7 @@
         <v>44581</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>46191</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>46190</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>46191</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>46191</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>46191</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>46190</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46191</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>46195</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>46196</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>45876</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45210</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45572</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>46197</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>46197</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>46197</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>46201</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>45551</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45628</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45351</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>46202</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45892,7 +45892,7 @@
         <v>46202</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45502</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>45188</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>45881</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>45614</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45645</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>46205</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45420</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>46205</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46549,7 +46549,7 @@
         <v>45196</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>44830</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46695,7 +46695,7 @@
         <v>45695</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>44617</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45607</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>46211</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45162</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47060,7 +47060,7 @@
         <v>45754</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>44859</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45215</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>46258</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>44699</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>45761</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47503,7 +47503,7 @@
         <v>45761</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>45090</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47654,7 +47654,7 @@
         <v>45775</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47727,7 +47727,7 @@
         <v>45153</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45531</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47873,7 +47873,7 @@
         <v>45404</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>46260</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>46260</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45198</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>46260</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45188</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>44781</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45203</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>45232</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>45190</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>46266</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48676,7 +48676,7 @@
         <v>45756</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45756</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>46220</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45247</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45245</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>46266</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45272</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>44838</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>44755</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49343,7 +49343,7 @@
         <v>44804</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>46268</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49489,7 +49489,7 @@
         <v>45162</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45477</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>44859</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>46274</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>45259</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49854,7 +49854,7 @@
         <v>46266</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49927,7 +49927,7 @@
         <v>46237</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
         <v>44900</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>46237</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50146,7 +50146,7 @@
         <v>46233</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         <v>46279</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>46239</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>46282</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>45520</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>46282</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45567</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>46282</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45167</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>45229</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>46286</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50974,7 +50974,7 @@
         <v>46286</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51052,7 +51052,7 @@
         <v>46286</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51130,7 +51130,7 @@
         <v>46286</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45008</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51276,7 +51276,7 @@
         <v>46287</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>46287</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51427,7 +51427,7 @@
         <v>44887</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>46288</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51578,7 +51578,7 @@
         <v>45188</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>46287</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>46245</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45376</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51870,7 +51870,7 @@
         <v>46244</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         <v>46184</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>46287</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>46287</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>46245</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>45036</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52313,7 +52313,7 @@
         <v>46246</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52386,7 +52386,7 @@
         <v>46246</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45551</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>46105</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>46290</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>46248</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52751,7 +52751,7 @@
         <v>46248</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52829,7 +52829,7 @@
         <v>44909</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>45590</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>45622</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>44953</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>44953</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>44957</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>44957</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>45637</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53423,7 +53423,7 @@
         <v>45572</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         <v>44900</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53569,7 +53569,7 @@
         <v>44725</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53647,7 +53647,7 @@
         <v>44515</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>44630</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53793,7 +53793,7 @@
         <v>45337</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53866,7 +53866,7 @@
         <v>45194</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53939,7 +53939,7 @@
         <v>45147</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45453</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>45299</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54158,7 +54158,7 @@
         <v>44865</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>44838</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45001</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54382,7 +54382,7 @@
         <v>45642</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>45615</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>45761</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54606,7 +54606,7 @@
         <v>44644</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45196</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>44937</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>45775</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54898,7 +54898,7 @@
         <v>45769</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45771</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45351</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55122,7 +55122,7 @@
         <v>45363</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45448</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45279</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55341,7 +55341,7 @@
         <v>45440</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55414,7 +55414,7 @@
         <v>45072</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45615</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>45568</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>45259</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         <v>45296</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>45497</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45632</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55925,7 +55925,7 @@
         <v>45756</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56003,7 +56003,7 @@
         <v>45749</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>45743</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56149,7 +56149,7 @@
         <v>45194</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56222,7 +56222,7 @@
         <v>45695</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45433</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56368,7 +56368,7 @@
         <v>45748</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56441,7 +56441,7 @@
         <v>45784</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56514,7 +56514,7 @@
         <v>45408</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56587,7 +56587,7 @@
         <v>45725</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45625</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>45625</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56806,7 +56806,7 @@
         <v>45232</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56879,7 +56879,7 @@
         <v>45638</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56952,7 +56952,7 @@
         <v>45785</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57025,7 +57025,7 @@
         <v>45625</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>45728</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57176,7 +57176,7 @@
         <v>44550</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>44602</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57332,7 +57332,7 @@
         <v>45341</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45315</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57483,7 +57483,7 @@
         <v>44893</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57561,7 +57561,7 @@
         <v>44522</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57639,7 +57639,7 @@
         <v>45258</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57712,7 +57712,7 @@
         <v>45616</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45881</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57868,7 +57868,7 @@
         <v>45915</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45679</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>46021</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>46035</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>46035</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>46043</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>46125</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -601,7 +601,7 @@
         <v>45763</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45118</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45737</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>45775</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46037</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45826</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>46213</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45932</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45666</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46071</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45826</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46201</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>45967</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45911</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>46246</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46248</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>46287</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45959</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45590</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45625</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>46230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>45992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45217</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45792</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46281</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46177</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46205</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>46281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45848</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45833</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45653</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45533</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>45003</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45925</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>45895</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45981</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45902</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46244</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>46112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>46036</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45264</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>46006</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45841</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46089</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>46178</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>46276</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>45623</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>46112</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>46078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>44725</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45982</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>46248</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44637</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>46105</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>46008</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45985</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>45833</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>45418</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45890</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>46085</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45481</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>45835</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45848</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>46202</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>46202</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>46206</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>46276</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>46237</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>46248</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>46248</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45782</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44545</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45967</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>45966</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45791</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>46008</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45320</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44881</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45699</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>44742</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45775</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45007</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>45090</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>46162</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>45852</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45159</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45180</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>46198</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45756</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45219</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45533</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>44589</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44470</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>45533</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>46029</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>44893</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>44959</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44897</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>45471</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>46006</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45826</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>44529</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>46237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45618</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45576</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44953</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45098</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45077</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45540</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45264</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>45377</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>46089</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44553</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44546</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>44813</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44515</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44832</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>44838</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44601</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44705</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>44516</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>44747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44848</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44673</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44788</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44489</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44609</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>44578</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44546</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>44530</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>44466</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44488</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>44480</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44749</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44589</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>44543</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>44680</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>44489</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>44858</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44796</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44810</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>44522</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>44656</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>44613</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>44726</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45334</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45412</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45222</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44847</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45460</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45253</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45420</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45210</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45425</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45415</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44497</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>44720</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44796</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>46014</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46013</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45715</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45954</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>46013</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44852</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>46024</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45524</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45272</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45049</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45791</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44874</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45174</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45798</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45755</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45797</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>45798</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>44531</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44482</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>44473</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>44819</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>46029</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45894</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45891</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45800</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45894</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>46041</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45499</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45896</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>45799</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>44898</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>46042</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45897</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>46044</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>44911</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>45898</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>46043</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>44581</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45460</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45901</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>44956</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45567</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45902</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>45904</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45646</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45911</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>46056</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>46057</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45912</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>46057</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45911</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>46059</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45916</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45617</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45667</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45551</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45917</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44945</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>46063</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46064</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45919</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>46065</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>46066</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>46072</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45925</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44942</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>46076</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45240</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>45929</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>45930</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>45929</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
         <v>46080</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45810</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45625</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45497</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45439</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45931</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>46084</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>46085</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>46085</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45931</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44995</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45404</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>45573</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>45931</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45576</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46091</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45810</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45938</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44694</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45937</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>46090</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>46091</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45691</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>45229</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>45938</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44907</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45937</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44897</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45554</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45203</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45057</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45574</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>46052</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45810</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>46098</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45184</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45615</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45952</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45279</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>46112</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45742</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45958</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45958</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45960</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45960</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45960</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45960</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45960</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45960</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>46121</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>46119</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>46119</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>44831</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>46119</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45961</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>46122</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45965</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45019</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45965</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46127</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45090</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>46127</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45968</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45705</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45967</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45812</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45967</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45966</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>45813</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45602</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>46126</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45145</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45631</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45474</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45977</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45979</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45980</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45979</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>46133</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45982</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45981</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>46105</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>46134</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>46106</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>44642</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45645</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>45820</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45632</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>45624</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>46119</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45988</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45184</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44768</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>46135</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45992</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45992</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45812</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>45968</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45992</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>45756</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>44658</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>45810</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44810</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>44517</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>45385</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>46062</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>45999</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44845</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45239</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45278</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45593</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>45463</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45205</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>46001</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>46001</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>44959</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>46002</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>46002</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>46002</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45981</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46006</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>46003</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>46006</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45820</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>46008</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>44482</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>46008</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>45188</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>46007</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45530</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46008</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45628</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>45820</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>45820</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>46009</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45807</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45562</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>45807</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>45544</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>46009</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46014</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45502</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45260</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45252</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45572</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>45821</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>46140</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>46048</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45063</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45826</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>45826</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44851</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>44533</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45985</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>46048</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45173</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45825</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>44518</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45834</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45775</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>46141</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>46142</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>46142</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46141</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45524</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>46141</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45476</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45476</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>46141</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45576</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>44484</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>46142</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45077</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>46141</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>46141</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>45334</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>46139</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>46051</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>46141</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>46146</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45831</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>46148</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>46148</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45232</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>46148</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>44806</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>46148</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>45264</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45264</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>44837</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46147</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>46147</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>45252</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45632</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45831</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45831</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45831</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>45253</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>46101</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45147</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45254</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45299</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45280</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>45757</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46153</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>44903</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45105</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>46155</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45296</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45520</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>46160</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>46160</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>46160</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>44915</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>45259</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>45761</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>46161</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45463</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45264</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>44896</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>46162</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>46161</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>46163</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>46164</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45846</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>45756</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>46163</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>45981</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>46094</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>46168</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45343</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46168</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45387</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>45855</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>45561</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>45259</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>45132</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>46170</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>46170</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45358</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45105</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>44600</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>45279</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>46170</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45159</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45505</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>45866</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>46174</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>45544</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44957</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>45104</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42902,7 +42902,7 @@
         <v>46163</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45999</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>45567</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>44589</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45692</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45771</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>46098</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45761</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>46182</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>46148</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>45410</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45611</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>46184</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>46185</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43939,7 +43939,7 @@
         <v>46188</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45072</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>46191</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>45874</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>46191</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44309,7 +44309,7 @@
         <v>44581</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>46191</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>46190</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>46191</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>46191</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>46191</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>46190</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46191</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>46195</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>46196</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>45876</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45210</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45572</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>46197</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>46197</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>46197</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>46201</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>45551</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45628</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45351</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>46202</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45892,7 +45892,7 @@
         <v>46202</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45502</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46038,7 +46038,7 @@
         <v>45188</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46111,7 +46111,7 @@
         <v>45881</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>45614</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45645</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         <v>46205</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46403,7 +46403,7 @@
         <v>45420</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>46205</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46549,7 +46549,7 @@
         <v>45196</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>44830</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46695,7 +46695,7 @@
         <v>45695</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>44617</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45607</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>46211</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45162</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47060,7 +47060,7 @@
         <v>45754</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>44859</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45215</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>46258</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>44699</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>45761</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47503,7 +47503,7 @@
         <v>45761</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>45090</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47654,7 +47654,7 @@
         <v>45775</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47727,7 +47727,7 @@
         <v>45153</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45531</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47873,7 +47873,7 @@
         <v>45404</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>46260</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>46260</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45198</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>46260</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45188</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>44781</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45203</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>45232</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>45190</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>46266</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48676,7 +48676,7 @@
         <v>45756</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45756</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>46220</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45247</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45245</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>46266</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45272</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>44838</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>44755</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49343,7 +49343,7 @@
         <v>44804</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>46268</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49489,7 +49489,7 @@
         <v>45162</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45477</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>44859</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>46274</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>45259</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49854,7 +49854,7 @@
         <v>46266</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49927,7 +49927,7 @@
         <v>46237</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
         <v>44900</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>46237</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50146,7 +50146,7 @@
         <v>46233</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         <v>46279</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>46239</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>46282</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>45520</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>46282</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45567</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>46282</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45167</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>45229</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>46286</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50974,7 +50974,7 @@
         <v>46286</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51052,7 +51052,7 @@
         <v>46286</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51130,7 +51130,7 @@
         <v>46286</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45008</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51276,7 +51276,7 @@
         <v>46287</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>46287</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51427,7 +51427,7 @@
         <v>44887</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>46288</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51578,7 +51578,7 @@
         <v>45188</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>46287</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>46245</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45376</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51870,7 +51870,7 @@
         <v>46244</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         <v>46184</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>46287</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>46287</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>46245</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>45036</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52313,7 +52313,7 @@
         <v>46246</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52386,7 +52386,7 @@
         <v>46246</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45551</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>46105</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>46290</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52678,7 +52678,7 @@
         <v>46248</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52751,7 +52751,7 @@
         <v>46248</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52829,7 +52829,7 @@
         <v>44909</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>45590</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>45622</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>44953</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>44953</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>44957</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>44957</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>45637</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53423,7 +53423,7 @@
         <v>45572</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         <v>44900</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53569,7 +53569,7 @@
         <v>44725</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53647,7 +53647,7 @@
         <v>44515</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>44630</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53793,7 +53793,7 @@
         <v>45337</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53866,7 +53866,7 @@
         <v>45194</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53939,7 +53939,7 @@
         <v>45147</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45453</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>45299</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54158,7 +54158,7 @@
         <v>44865</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>44838</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45001</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54382,7 +54382,7 @@
         <v>45642</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>45615</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>45761</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54606,7 +54606,7 @@
         <v>44644</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45196</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>44937</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>45775</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54898,7 +54898,7 @@
         <v>45769</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45771</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45351</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55122,7 +55122,7 @@
         <v>45363</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45448</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>45279</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55341,7 +55341,7 @@
         <v>45440</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55414,7 +55414,7 @@
         <v>45072</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>45615</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55560,7 +55560,7 @@
         <v>45568</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>45259</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55706,7 +55706,7 @@
         <v>45296</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>45497</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45632</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55925,7 +55925,7 @@
         <v>45756</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56003,7 +56003,7 @@
         <v>45749</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>45743</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56149,7 +56149,7 @@
         <v>45194</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56222,7 +56222,7 @@
         <v>45695</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45433</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56368,7 +56368,7 @@
         <v>45748</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56441,7 +56441,7 @@
         <v>45784</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56514,7 +56514,7 @@
         <v>45408</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56587,7 +56587,7 @@
         <v>45725</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45625</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>45625</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56806,7 +56806,7 @@
         <v>45232</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56879,7 +56879,7 @@
         <v>45638</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56952,7 +56952,7 @@
         <v>45785</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57025,7 +57025,7 @@
         <v>45625</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>45728</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57176,7 +57176,7 @@
         <v>44550</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>44602</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57332,7 +57332,7 @@
         <v>45341</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45315</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57483,7 +57483,7 @@
         <v>44893</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57561,7 +57561,7 @@
         <v>44522</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57639,7 +57639,7 @@
         <v>45258</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57712,7 +57712,7 @@
         <v>45616</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45881</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57868,7 +57868,7 @@
         <v>45915</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45679</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>46021</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>46035</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>46035</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>46043</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>46125</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -601,7 +601,7 @@
         <v>45763</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45118</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45737</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>45775</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46037</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45826</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>46213</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45932</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45666</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46071</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45826</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46201</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>45967</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
         <v>18</v>
       </c>
       <c r="T16" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="U16" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45911</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>46246</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46248</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>46287</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45959</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45590</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45625</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>46230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>45992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45217</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45792</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46281</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46205</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>46281</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45848</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>46177</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45653</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45833</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45533</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>45003</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45925</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>45895</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45981</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45902</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46244</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>46112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>46036</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45264</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>46006</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45841</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46089</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>46178</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>46276</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>45623</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>46112</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>46078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45982</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44725</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>46248</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44637</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>46008</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>46105</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45833</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>45985</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>46297</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44796</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45890</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>46085</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45835</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45848</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>46202</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>46202</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>46206</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46276</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>46237</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>46248</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>46248</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>45481</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>45418</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45782</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44545</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>46008</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45966</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45967</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>45791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>45320</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44881</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45699</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>44742</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>45533</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45219</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45159</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45852</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>46162</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45756</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>46198</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45180</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45007</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45090</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45775</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>44589</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>46006</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>46029</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44959</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>45471</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45826</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44893</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44529</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44897</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45077</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>46237</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45098</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45576</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45540</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44953</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45618</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45264</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45377</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>46089</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44553</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44813</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>44546</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44515</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>44832</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44838</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>44601</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>44705</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44516</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>44747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44848</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44673</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>44489</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>44788</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44609</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>44578</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44546</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44530</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>44488</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44480</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44749</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>44589</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44543</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44680</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>44489</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44858</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44796</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44810</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>44522</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>44613</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>44656</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44726</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45530</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45637</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45692</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45756</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>45351</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45351</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>44630</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44874</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>45590</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45572</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45642</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45264</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45743</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>45167</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>45568</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>46001</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45622</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>44531</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>46002</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>46002</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>46002</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>46003</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>45757</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45625</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>46006</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45625</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>46006</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45785</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44768</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>44852</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>46007</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>46009</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>46009</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>46008</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>46008</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45602</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>46008</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45807</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>45807</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>46013</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45638</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45954</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>46013</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>46014</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45725</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>46014</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44896</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45891</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45891</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>46024</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45800</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45894</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45695</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45894</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45184</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>44810</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>45896</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45897</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45799</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>45280</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45412</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44956</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>45625</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>45898</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44859</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45901</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44581</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45902</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45902</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45749</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>46029</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44482</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45904</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44720</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44995</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>46041</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46042</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45240</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44959</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45232</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45791</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44898</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45272</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>46043</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45797</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45715</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44796</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45049</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45911</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>46044</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45912</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45090</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45916</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45798</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45253</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45917</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45798</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>44473</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44518</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45919</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45194</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45497</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45810</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>46057</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45924</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>46056</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45925</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>46057</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45439</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45625</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>45929</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45929</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45911</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>46059</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45810</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45930</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45931</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>46063</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44831</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>46064</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>46065</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>45132</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45645</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>46066</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45159</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45931</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45705</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45931</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45937</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45937</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45104</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45938</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45938</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45810</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45019</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45232</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44484</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>46072</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46076</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45090</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>46080</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45279</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>46084</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45952</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45433</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45453</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44617</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>46085</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45813</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45812</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>46085</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>46090</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45958</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45958</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45232</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>45742</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45961</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45960</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45960</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>45960</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45960</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45960</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45463</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>46091</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45960</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>46091</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>44903</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>46052</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>45965</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45965</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45420</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>45966</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45967</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45259</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45967</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>45646</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45259</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>46098</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44942</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>45968</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45611</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>44755</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>45667</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45977</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>45979</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45979</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>45299</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45981</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>45775</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45980</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>45615</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>45821</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>45820</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>45982</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>46112</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45820</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45820</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>45617</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45968</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>46119</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45825</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>46119</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45988</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>46119</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>45992</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>46121</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44907</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>46122</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45245</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>45992</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>45992</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44781</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45531</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45387</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46126</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>45593</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>45205</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45999</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>46127</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45239</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45278</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45463</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>46127</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>45826</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45826</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>46001</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45831</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45831</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45477</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45077</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>46134</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45252</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>46135</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45831</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45831</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>46106</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>46133</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>46105</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45834</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44847</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>44830</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>45810</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45981</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45404</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>46062</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44900</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45628</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45820</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>44911</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>45985</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>45624</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44517</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45544</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>45846</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45296</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>44845</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>45505</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>44658</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>44497</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45260</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45502</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44909</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44644</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>46048</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>46119</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>44865</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45812</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45252</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45855</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45748</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>45198</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45358</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45562</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45761</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>45190</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>46141</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>46141</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>45551</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>44897</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45497</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45385</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>44600</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>46140</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>46141</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>46141</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>46141</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>46141</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45866</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45474</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45551</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45460</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45576</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>44725</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>46048</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>44837</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45615</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>45188</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45775</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>46142</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46142</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>46142</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45771</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>46147</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>46147</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>46141</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45761</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>46139</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>46051</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>46148</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>46148</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>46148</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>45502</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>45296</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45299</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>44859</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45771</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45874</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45259</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45229</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>46153</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>45001</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>45147</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45072</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>45254</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>46101</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45063</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>46155</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45188</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45572</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>44900</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>46161</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>46160</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>45769</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>46161</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>46160</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45337</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>46160</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45876</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>46163</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>46162</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>46163</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45196</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>46164</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>46094</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45203</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>46168</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45981</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>46168</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>45524</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>46170</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>46170</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>46170</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>46174</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>44804</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45881</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45614</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>45755</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45645</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>45999</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>46098</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45222</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>45404</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>46163</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45145</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>46182</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>46148</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45574</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>46184</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>46188</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>44915</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>46185</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>44482</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45210</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45153</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>46190</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>44515</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>46190</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>46191</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>46191</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45632</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>46191</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>46191</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>46191</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>46191</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>46191</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45756</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45057</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>45036</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>45188</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>46195</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         <v>44581</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>46196</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45628</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>45196</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45775</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>46197</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>46197</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>46197</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>46201</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47502,7 +47502,7 @@
         <v>46202</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>44699</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>46202</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>46205</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>46205</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>45162</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>45279</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>44945</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45184</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>46211</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>46258</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>44957</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>44957</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45203</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>46260</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>46260</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45105</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45425</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>46260</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>45147</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48972,7 +48972,7 @@
         <v>45253</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>46220</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>44887</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>46266</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45173</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>45691</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>46266</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>46268</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45573</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45761</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45247</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>46266</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45567</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45415</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>45210</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45105</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>46274</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>46233</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45499</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45420</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>45554</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>46279</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>46237</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45174</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>46237</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>46239</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>44838</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50963,7 +50963,7 @@
         <v>45695</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>46282</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>46282</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>46282</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>45334</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>46244</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51416,7 +51416,7 @@
         <v>46286</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51494,7 +51494,7 @@
         <v>46287</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51567,7 +51567,7 @@
         <v>44838</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>46286</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>46287</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>44642</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>46287</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>46287</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>46286</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52093,7 +52093,7 @@
         <v>46286</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>46184</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>46287</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45756</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>46245</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45524</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>46288</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45544</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45343</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45072</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>46245</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>46246</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>46246</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45754</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>46248</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>46248</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>45215</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45476</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
         <v>45476</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>46290</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>46105</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45460</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>44957</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53782,7 +53782,7 @@
         <v>45567</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53855,7 +53855,7 @@
         <v>45363</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>46293</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45440</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54074,7 +54074,7 @@
         <v>45632</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54147,7 +54147,7 @@
         <v>46295</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>46297</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45576</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54381,7 +54381,7 @@
         <v>45632</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>44953</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>44953</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>45631</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54673,7 +54673,7 @@
         <v>44819</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54746,7 +54746,7 @@
         <v>45272</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>45376</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>44937</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>44806</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>44533</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45279</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45229</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45615</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>45008</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>45761</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55481,7 +55481,7 @@
         <v>45761</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55559,7 +55559,7 @@
         <v>44589</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55632,7 +55632,7 @@
         <v>45194</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45756</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55783,7 +55783,7 @@
         <v>45162</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55856,7 +55856,7 @@
         <v>45259</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45756</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45188</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45448</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>44694</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56226,7 +56226,7 @@
         <v>44851</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56299,7 +56299,7 @@
         <v>45334</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>45520</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56450,7 +56450,7 @@
         <v>45520</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56523,7 +56523,7 @@
         <v>45561</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56596,7 +56596,7 @@
         <v>45572</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56669,7 +56669,7 @@
         <v>45607</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56742,7 +56742,7 @@
         <v>45567</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56815,7 +56815,7 @@
         <v>45410</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45264</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45264</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45551</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57117,7 +57117,7 @@
         <v>45408</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45784</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57263,7 +57263,7 @@
         <v>45728</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>45341</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57414,7 +57414,7 @@
         <v>45315</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57492,7 +57492,7 @@
         <v>44893</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57570,7 +57570,7 @@
         <v>44522</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57648,7 +57648,7 @@
         <v>44550</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57726,7 +57726,7 @@
         <v>45258</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57799,7 +57799,7 @@
         <v>44602</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>45616</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45881</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58033,7 +58033,7 @@
         <v>45915</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58111,7 +58111,7 @@
         <v>45679</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58184,7 +58184,7 @@
         <v>46021</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58257,7 +58257,7 @@
         <v>46035</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>46035</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58413,7 +58413,7 @@
         <v>46043</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58491,7 +58491,7 @@
         <v>46125</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -601,7 +601,7 @@
         <v>45763</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45118</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45737</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>45775</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46037</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45826</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>46213</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45932</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45666</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46071</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45826</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46201</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>45967</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45911</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>46246</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>46248</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>46287</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45959</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45590</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45625</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>46230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>45992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45217</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45792</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46281</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46205</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>46281</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45848</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>46177</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45653</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45833</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45533</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>46167</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>45003</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45925</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>45895</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45981</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>45902</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46244</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>46112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>46036</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45264</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>46006</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>46206</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45841</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46089</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45525</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>46178</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>46276</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>45623</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>46112</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>46078</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45982</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>44725</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>46248</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44637</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>46008</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>46105</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45833</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>45985</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>46297</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44796</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45890</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>46085</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45835</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45848</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>46202</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>46202</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>46206</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46276</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>46237</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>46248</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>46248</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>45481</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>45418</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45782</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44545</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>46008</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45966</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45967</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>45791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>45320</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44881</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45699</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>44742</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>45533</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45219</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45159</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45852</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>46162</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45756</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>46198</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45180</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45007</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45090</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45775</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>44589</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>46006</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>46029</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44959</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>45471</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45826</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44893</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44529</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>44897</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45077</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>46237</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45098</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45576</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45540</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44953</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45618</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45264</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45377</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>46089</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44553</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44813</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>44546</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44515</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>44832</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44838</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>44601</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>44705</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44516</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>44747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44848</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44673</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>44489</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>44788</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44609</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>44578</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44546</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44530</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>44488</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44480</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44749</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>44589</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44543</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44680</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>44489</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44858</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44796</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44810</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>44522</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>44613</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>44656</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>44726</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45530</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45637</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45692</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45756</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>45351</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45351</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>44630</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44874</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>45590</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45572</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45642</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45264</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45743</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>45167</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>45568</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>46001</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45622</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>44531</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>46002</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>46002</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>46002</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>46003</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>45757</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45625</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>46006</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45625</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>46006</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45785</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44768</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>44852</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>46007</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>46009</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>46009</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>46008</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>46008</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45602</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>46008</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45807</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>45807</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>46013</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45638</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45954</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>46013</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>46014</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45725</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>46014</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44896</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45891</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45891</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>46024</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45800</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45894</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45695</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45894</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45184</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>44810</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21992,7 +21992,7 @@
         <v>45896</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45897</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45799</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>45280</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45412</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44956</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>45625</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>45898</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44859</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45901</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44581</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45902</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45902</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45749</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>46029</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44482</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45904</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44720</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44995</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>46041</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46042</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45240</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44959</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45232</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45791</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44898</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45272</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>46043</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45797</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45715</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44796</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45049</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45911</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>46044</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45912</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45090</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45916</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45798</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45253</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45917</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45798</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>44473</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44518</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45919</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45194</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45497</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45810</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>46057</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45924</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>46056</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45925</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>46057</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45439</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45625</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>45929</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45929</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45911</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>46059</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45810</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45930</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45931</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>46063</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44831</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>46064</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>46065</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>45132</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45645</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>46066</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45159</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45931</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45705</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45931</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45937</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45937</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45104</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45938</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45938</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45810</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45019</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45232</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44484</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>46072</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46076</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45090</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>46080</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45279</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>46084</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45952</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45433</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45453</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44617</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>46085</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45813</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45812</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>46085</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>46090</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45958</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45958</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45232</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>45742</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45961</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45960</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45960</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>45960</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45960</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45960</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45463</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>46091</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45960</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>46091</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>44903</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>46052</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>45965</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45965</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45420</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>45966</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45967</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45259</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45967</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>45646</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45259</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>46098</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44942</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>45968</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45611</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>44755</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>45667</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45977</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>45979</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45979</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>45299</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45981</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>45775</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45980</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>45615</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>45821</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>45820</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>45982</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>46112</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45820</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45820</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>45617</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45968</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>46119</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45825</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>46119</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45988</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>46119</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>45992</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>46121</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>44907</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>46122</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45245</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>45992</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>45992</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44781</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45531</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45387</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46126</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>45593</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>45205</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45999</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>46127</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45239</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45278</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45463</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>46127</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>45826</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45826</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>46001</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45831</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45831</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45477</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45077</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>46134</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45252</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>46135</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45831</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45831</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>46106</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>46133</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>46105</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45834</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44847</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>44830</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>45810</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45981</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45404</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>46062</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>44900</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45628</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45820</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>44911</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>45985</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>45624</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44517</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45544</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>45846</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45296</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>44845</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>45505</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>44658</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>44497</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45260</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45502</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44909</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>44644</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>46048</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>46119</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>44865</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45812</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45252</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45855</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45748</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>45198</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45358</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45562</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45761</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>45190</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>46141</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>46141</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>45551</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>44897</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45497</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45385</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>44600</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>46140</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>46141</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>46141</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>46141</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>46141</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45866</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45474</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45551</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45460</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45576</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>44725</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>46048</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>44837</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45615</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>45188</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45775</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>46142</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46142</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>46142</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45771</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>46147</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>46147</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>46141</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45761</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>46139</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>46051</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>46148</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>46148</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>46148</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>45502</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>45296</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45299</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>44859</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45771</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45874</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45259</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45229</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>46153</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>45001</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>45147</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45072</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>45254</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>46101</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45063</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>46155</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45188</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45572</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>44900</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>46161</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>46160</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>45769</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>46161</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>46160</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45337</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>46160</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45876</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>46163</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>46162</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>46163</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45196</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>46164</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>46094</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45203</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>46168</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45981</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>46168</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43694,7 +43694,7 @@
         <v>45524</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>46170</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>46170</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>46170</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>46174</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>44804</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45881</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45614</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>45755</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45645</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>45999</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>46098</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45222</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>45404</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>46163</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45145</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>46182</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>46148</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45574</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>46184</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>46188</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>44915</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>46185</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>44482</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45210</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45153</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>46190</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>44515</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>46190</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>46191</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>46191</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45632</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>46191</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>46191</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>46191</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>46191</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>46191</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45756</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45057</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>45036</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>45188</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>46195</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         <v>44581</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>46196</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45628</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>45196</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45775</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>46197</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>46197</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>46197</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>46201</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47502,7 +47502,7 @@
         <v>46202</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>44699</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>46202</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>46205</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>46205</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>45162</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>45279</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>44945</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45184</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>46211</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>46258</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>44957</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>44957</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45203</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>46260</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>46260</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45105</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45425</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>46260</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>45147</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48972,7 +48972,7 @@
         <v>45253</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>46220</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>44887</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>46266</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45173</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>45691</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>46266</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49493,7 +49493,7 @@
         <v>46268</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45573</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>45761</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45247</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>46266</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45567</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45415</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>45210</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45105</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>46274</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>46233</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45499</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45420</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>45554</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>46279</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>46237</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45174</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>46237</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>46239</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>44838</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50963,7 +50963,7 @@
         <v>45695</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>46282</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>46282</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>46282</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>45334</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>46244</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51416,7 +51416,7 @@
         <v>46286</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51494,7 +51494,7 @@
         <v>46287</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51567,7 +51567,7 @@
         <v>44838</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>46286</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51718,7 +51718,7 @@
         <v>46287</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>44642</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>46287</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>46287</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>46286</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52093,7 +52093,7 @@
         <v>46286</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>46184</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>46287</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45756</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>46245</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45524</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>46288</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45544</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>45343</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45072</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>46245</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>46246</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>46246</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>45754</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>46248</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>46248</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>45215</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45476</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
         <v>45476</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>46290</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>46105</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>45460</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>44957</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53782,7 +53782,7 @@
         <v>45567</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53855,7 +53855,7 @@
         <v>45363</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>46293</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45440</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54074,7 +54074,7 @@
         <v>45632</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54147,7 +54147,7 @@
         <v>46295</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>46297</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45576</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54381,7 +54381,7 @@
         <v>45632</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>44953</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>44953</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>45631</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54673,7 +54673,7 @@
         <v>44819</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54746,7 +54746,7 @@
         <v>45272</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>45376</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>44937</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>44806</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>44533</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45279</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45229</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45615</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>45008</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>45761</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55481,7 +55481,7 @@
         <v>45761</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55559,7 +55559,7 @@
         <v>44589</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55632,7 +55632,7 @@
         <v>45194</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45756</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55783,7 +55783,7 @@
         <v>45162</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55856,7 +55856,7 @@
         <v>45259</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>45756</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45188</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45448</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>44694</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56226,7 +56226,7 @@
         <v>44851</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56299,7 +56299,7 @@
         <v>45334</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>45520</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56450,7 +56450,7 @@
         <v>45520</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56523,7 +56523,7 @@
         <v>45561</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56596,7 +56596,7 @@
         <v>45572</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56669,7 +56669,7 @@
         <v>45607</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56742,7 +56742,7 @@
         <v>45567</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56815,7 +56815,7 @@
         <v>45410</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45264</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45264</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>45551</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57117,7 +57117,7 @@
         <v>45408</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45784</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57263,7 +57263,7 @@
         <v>45728</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>45341</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57414,7 +57414,7 @@
         <v>45315</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57492,7 +57492,7 @@
         <v>44893</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57570,7 +57570,7 @@
         <v>44522</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57648,7 +57648,7 @@
         <v>44550</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57726,7 +57726,7 @@
         <v>45258</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57799,7 +57799,7 @@
         <v>44602</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>45616</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45881</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58033,7 +58033,7 @@
         <v>45915</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58111,7 +58111,7 @@
         <v>45679</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58184,7 +58184,7 @@
         <v>46021</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58257,7 +58257,7 @@
         <v>46035</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>46035</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58413,7 +58413,7 @@
         <v>46043</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58491,7 +58491,7 @@
         <v>46125</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -601,7 +601,7 @@
         <v>45763</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45118</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45737</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>45775</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46037</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>46213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45932</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45666</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46071</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45826</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46201</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>45967</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45911</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>46287</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>46246</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>46248</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45959</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45590</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45625</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>46230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>45992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45217</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45792</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46281</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46205</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>46281</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>46177</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45848</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45653</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45833</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>46303</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45533</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>46167</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45003</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45925</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>45895</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45981</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45902</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>46112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>45264</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>46036</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>46006</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>46206</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45841</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>46089</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>45525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>46178</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>46198</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>46276</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>46260</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>46248</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>45623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>46112</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44725</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>46078</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45982</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>45848</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>46303</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>46248</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44637</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>46105</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>46008</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45985</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>45833</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>46297</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44796</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45418</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45890</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>45481</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>45835</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>46085</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>45848</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>46202</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>46202</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>46206</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>46276</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>46237</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>46248</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>46248</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>46260</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45782</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44545</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45967</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45966</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45320</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>46008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>45791</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44881</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>44742</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>45090</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45533</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>45159</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45180</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45756</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45852</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45775</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45007</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>46162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>46198</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44589</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45077</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44893</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>44529</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44959</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45471</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45826</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45618</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45576</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>44953</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>46006</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>46029</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45098</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>46237</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>46301</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>45264</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45377</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>46089</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44553</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>44546</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>44813</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44515</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>44832</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>44838</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44601</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>44705</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44516</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44747</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44848</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>44844</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44673</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44788</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>44489</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>44523</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>44609</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>44589</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>44480</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>44543</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44680</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44749</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>44578</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44489</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44488</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44796</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44546</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44530</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>44858</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44810</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>44522</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44656</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>44613</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45232</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44806</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44726</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45264</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45264</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>44837</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45252</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45632</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45412</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45222</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44838</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>44847</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45253</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>45299</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45757</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45415</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45001</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45642</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45615</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44903</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45105</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45296</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>45761</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44644</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45520</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45196</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>44937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45334</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45775</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44915</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45769</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45259</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45761</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45460</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45463</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45253</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45264</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45771</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44896</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45420</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45351</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45210</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45363</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45448</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45425</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45756</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45614</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45645</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45279</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45440</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44497</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45343</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45387</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45561</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45072</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45615</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>44852</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45755</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45259</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45132</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45568</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45105</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45524</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44600</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45259</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45296</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45279</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>44874</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45159</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45505</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45174</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45894</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45891</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45800</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45891</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45894</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45896</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45799</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45897</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45898</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>44581</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>44531</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>44482</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45902</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45497</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45901</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45632</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45756</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>44819</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44956</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45749</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>45743</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45194</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45544</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45695</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>45433</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44957</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45748</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45902</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45904</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45104</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45499</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>44898</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>44911</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45460</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45567</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45911</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>44589</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45692</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45771</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45567</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45761</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45912</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>45784</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45646</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>45916</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>45410</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45611</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45408</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45917</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45617</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45667</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>45551</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45919</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>44945</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>44581</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45725</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45924</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45925</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45625</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45625</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>44942</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45210</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45232</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45638</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45785</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>45572</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45240</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45929</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45625</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>44720</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>44796</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>45930</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>45929</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45715</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45551</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45628</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>45272</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>45049</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>45791</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>45351</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44995</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45931</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45798</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>45404</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45573</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45576</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45797</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45798</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45931</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45502</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45188</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44694</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45691</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45229</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>44907</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44897</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45420</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45554</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45931</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45203</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45057</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45574</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45938</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>45937</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>45184</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45196</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45810</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>45615</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45625</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45497</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45938</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>44830</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45439</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45810</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45937</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45810</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45695</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44617</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45742</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45607</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45705</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>45279</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45812</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>45813</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45162</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>45754</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44859</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45215</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>44699</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45761</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>45761</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45090</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45820</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45775</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33543,7 +33543,7 @@
         <v>45820</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>45820</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>45153</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45821</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44831</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45826</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45826</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>45019</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45825</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45952</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45090</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45531</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45404</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>45831</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45198</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45831</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45831</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45831</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45958</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45602</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45958</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45960</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>45960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45960</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45960</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45960</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>45960</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45145</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>45631</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45188</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45474</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>45961</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45965</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>44781</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45965</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45203</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>45968</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44642</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45645</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45967</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>45967</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45632</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>45966</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>45232</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45184</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45846</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>44768</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45190</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>45756</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45756</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45247</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>45245</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>45272</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45756</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>44838</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>44755</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44810</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45855</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44804</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45358</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>45866</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>44959</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45162</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>45977</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45979</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>45980</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>44482</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45477</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45530</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45979</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44859</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45072</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45874</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38922,7 +38922,7 @@
         <v>45876</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>45982</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>45502</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45981</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>45572</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>45881</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45259</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>46052</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>45063</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>46098</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>44851</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>44533</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45173</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44518</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>44900</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>45520</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45524</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45476</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>45476</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>45567</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>44484</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40460,7 +40460,7 @@
         <v>45077</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>45167</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>45229</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>45988</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>45334</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45992</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45992</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>46112</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45968</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>45992</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>46121</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>46119</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>46119</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>46119</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>46122</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>46127</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>46127</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45999</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45239</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45278</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>45593</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45463</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>45205</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>46001</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>46126</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>45008</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>46001</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44887</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>45188</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45376</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>46002</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>46002</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>46002</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>46133</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>46006</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>46003</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>46105</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>46134</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>45036</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>46006</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>46106</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45820</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>46008</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>46008</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>46007</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45624</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>46008</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>45551</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>46119</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>46009</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45807</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>46135</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>45812</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>45807</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>46009</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>46014</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>44658</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45810</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>46014</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>46013</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45954</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>46013</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45031,7 +45031,7 @@
         <v>44517</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45385</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45177,7 +45177,7 @@
         <v>46062</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>46024</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>44909</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45396,7 +45396,7 @@
         <v>44845</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45590</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45622</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44953</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44953</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>44957</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45834,7 +45834,7 @@
         <v>44957</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45981</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>45188</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45628</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45637</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>45562</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46282,7 +46282,7 @@
         <v>46029</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>45572</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45544</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>46041</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>44900</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>46042</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>44725</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>45260</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46876,7 +46876,7 @@
         <v>46044</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>44515</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>45252</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>46043</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>44630</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45337</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45194</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45147</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>46140</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>46048</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45453</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47679,7 +47679,7 @@
         <v>45985</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>46048</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45834</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>45299</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45775</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>46141</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>44865</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>46141</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>46056</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>46141</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48409,7 +48409,7 @@
         <v>46057</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>46057</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45911</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>46059</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>46141</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>45576</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>46142</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>46141</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>46141</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>46139</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49144,7 +49144,7 @@
         <v>46051</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>46063</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>46141</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49368,7 +49368,7 @@
         <v>46064</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>46146</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49514,7 +49514,7 @@
         <v>46148</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>46148</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>46065</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>46148</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>46148</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>46066</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>46147</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>46147</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>46072</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>46101</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45147</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>45254</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>46076</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>46153</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>46080</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>46084</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>46085</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>46085</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>46155</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>46160</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>46091</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>46160</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51175,7 +51175,7 @@
         <v>46090</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>46091</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>46160</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>46161</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51472,7 +51472,7 @@
         <v>46162</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>46161</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>46163</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>46164</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>46163</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45981</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>46094</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51993,7 +51993,7 @@
         <v>46168</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>46168</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>46170</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>46170</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>46170</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>46174</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>46163</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>46098</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>46182</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>46148</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>46184</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52816,7 +52816,7 @@
         <v>46185</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>46188</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52967,7 +52967,7 @@
         <v>46191</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>46191</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>46191</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53196,7 +53196,7 @@
         <v>46190</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53274,7 +53274,7 @@
         <v>46191</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53352,7 +53352,7 @@
         <v>46191</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>46191</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>46190</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>46191</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53664,7 +53664,7 @@
         <v>46195</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>46196</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>46197</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>46197</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53966,7 +53966,7 @@
         <v>46197</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54044,7 +54044,7 @@
         <v>46201</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>46202</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>46202</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54263,7 +54263,7 @@
         <v>46205</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54336,7 +54336,7 @@
         <v>46205</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>46211</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>46266</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>46220</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>46266</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>46268</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>46274</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54847,7 +54847,7 @@
         <v>46266</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>46237</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>46237</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>46233</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55144,7 +55144,7 @@
         <v>46279</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>46239</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>46282</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55368,7 +55368,7 @@
         <v>46282</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55446,7 +55446,7 @@
         <v>46282</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>46286</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>46286</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>46286</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>46286</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>46287</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>46287</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55982,7 +55982,7 @@
         <v>46288</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56055,7 +56055,7 @@
         <v>46287</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56128,7 +56128,7 @@
         <v>46245</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56201,7 +56201,7 @@
         <v>46244</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>46184</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>46287</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56425,7 +56425,7 @@
         <v>46287</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56498,7 +56498,7 @@
         <v>46245</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>46246</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>46246</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>46105</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>46290</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>46248</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>46293</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>46248</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>46295</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>46297</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57243,7 +57243,7 @@
         <v>46258</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>46301</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57394,7 +57394,7 @@
         <v>46303</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57467,7 +57467,7 @@
         <v>46303</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>46260</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57613,7 +57613,7 @@
         <v>46304</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45999</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>46303</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>45728</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57910,7 +57910,7 @@
         <v>44550</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>44602</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58066,7 +58066,7 @@
         <v>45341</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58139,7 +58139,7 @@
         <v>45315</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>44893</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>44522</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58373,7 +58373,7 @@
         <v>45258</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45616</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>45881</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58602,7 +58602,7 @@
         <v>45915</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>45679</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>46021</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>46035</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58904,7 +58904,7 @@
         <v>46035</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         <v>46043</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>46125</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -601,7 +601,7 @@
         <v>45763</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45118</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45737</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>45775</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46037</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>46213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45982</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45932</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>45666</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46071</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45826</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>46201</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>45967</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
         <v>18</v>
       </c>
       <c r="T16" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="U16" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45911</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>45919</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>46287</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>46246</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>46248</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45959</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45590</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45625</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>46230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>45992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45217</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45792</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46281</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46205</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>46281</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>46177</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>45848</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45653</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45833</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>46303</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45533</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>46167</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>45003</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45925</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>45895</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45981</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45902</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>46112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>45264</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>46036</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>46006</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>46206</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45841</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>46089</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>45525</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>46178</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>46198</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>46276</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>46260</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>46248</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>45623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>46112</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44725</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>46078</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45982</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>45848</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>46303</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>46248</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44637</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>46105</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>46008</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45985</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>45833</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>46297</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44796</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45418</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45890</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>45481</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>45835</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>46085</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>45848</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>46202</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>46202</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>46206</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>46276</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>46237</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>46248</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>46248</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>46260</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45782</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44545</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45967</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45966</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45320</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>46008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>45791</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44881</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>44742</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>45090</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45533</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>45159</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45180</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>45756</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45852</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45775</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45007</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>46162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>46198</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44589</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45077</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44893</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>44529</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44959</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45471</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45826</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45618</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45576</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>44953</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>46006</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>46029</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45098</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>46237</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>46301</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>45264</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45377</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>46089</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44553</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>44546</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>44813</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>44515</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>44832</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>44838</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44601</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>44705</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44516</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44747</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44848</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>44844</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44673</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44788</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>44489</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>44523</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>44609</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>44589</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>44480</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>44543</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44680</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44749</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>44578</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44489</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44488</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44796</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44546</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44530</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>44858</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44810</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>44522</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44656</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>44613</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45232</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44806</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44726</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45264</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45264</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>44837</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45252</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45632</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45412</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45222</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44838</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>44847</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45253</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>45299</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45757</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45415</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45001</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45642</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45615</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44903</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45105</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45296</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>45761</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44644</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45520</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45196</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>44937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45334</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45775</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44915</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45769</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45259</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45761</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45460</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45463</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45253</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45264</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45771</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>44896</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45420</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45351</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45210</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45363</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45448</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45425</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45756</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45614</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45645</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45279</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45440</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44497</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45343</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45387</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45561</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45072</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45615</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>44852</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45755</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45259</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45132</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45568</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45105</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45524</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44600</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45259</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45296</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45279</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>44874</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45159</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45505</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45174</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45894</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45891</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45800</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45891</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45894</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45896</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45799</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45897</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45898</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>44581</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>44531</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>44482</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45902</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45497</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45901</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45632</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45756</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>44819</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44956</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45749</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>45743</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45194</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45544</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45695</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>45433</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44957</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45748</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45902</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45904</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45104</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45499</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>44898</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>44911</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45460</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45567</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45911</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>44589</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45692</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45771</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45567</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45761</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45912</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>45784</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45646</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>45916</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>45410</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45611</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45408</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45917</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45617</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45667</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>45551</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45919</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>44945</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>44581</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45725</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45924</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45925</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45625</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45625</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>44942</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45210</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45232</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45638</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45785</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>45572</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45240</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45929</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45625</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>44720</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>44796</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>45930</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>45929</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45715</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45551</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45628</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>45272</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>45049</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>45791</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>45351</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44995</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45931</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45798</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>45404</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45573</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45576</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45797</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45798</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45931</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45502</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45188</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44694</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45691</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45229</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>44907</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44897</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45420</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45554</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45931</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45203</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45057</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45574</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45938</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>45937</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>45184</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45196</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45810</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>45615</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31620,7 +31620,7 @@
         <v>45625</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>45497</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45938</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>44830</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45439</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45810</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45937</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45810</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45695</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44617</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45742</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45607</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45705</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>45279</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45812</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>45813</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45162</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>45754</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44859</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45215</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>44699</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45761</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>45761</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45090</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45820</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45775</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33543,7 +33543,7 @@
         <v>45820</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>45820</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>45153</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45821</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44831</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45826</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45826</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>45019</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45825</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45952</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45090</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45531</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45404</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>45831</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45198</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45831</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45831</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45831</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45958</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45602</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45958</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45960</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>45960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45960</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45960</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45960</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>45960</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45145</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>45631</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45188</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45474</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>45961</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45965</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>44781</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45965</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45203</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>45968</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44642</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45645</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45967</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>45967</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45632</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>45966</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>45232</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45184</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45846</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>44768</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45190</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>45756</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45756</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45247</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>45245</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>45272</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45756</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>44838</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>44755</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44810</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45855</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44804</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45358</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>45866</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>44959</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45162</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>45977</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45979</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>45980</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>44482</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45477</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45530</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45979</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44859</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45072</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45874</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38922,7 +38922,7 @@
         <v>45876</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>45982</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>45502</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45981</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>45572</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>45881</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45259</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>46052</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>45063</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>46098</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>44851</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>44533</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45173</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44518</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>44900</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>45520</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45524</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45476</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>45476</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>45567</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>44484</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40460,7 +40460,7 @@
         <v>45077</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>45167</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>45229</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>45988</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>45334</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45992</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45992</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>46112</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45968</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>45992</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>46121</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>46119</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>46119</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>46119</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>46122</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>46127</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>46127</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45999</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45239</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45278</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>45593</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45463</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>45205</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>46001</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>46126</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>45008</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>46001</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44887</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>45188</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45376</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>46002</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>46002</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>46002</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>46133</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>46006</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>46003</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>46105</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>46134</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>45036</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>46006</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>46106</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45820</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>46008</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>46008</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>46007</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45624</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>46008</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>45551</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>46119</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>46009</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45807</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>46135</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>45812</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>45807</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>46009</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>46014</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>44658</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45810</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>46014</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>46013</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45954</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>46013</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45031,7 +45031,7 @@
         <v>44517</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45385</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45177,7 +45177,7 @@
         <v>46062</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>46024</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>44909</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45396,7 +45396,7 @@
         <v>44845</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45590</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45622</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>44953</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44953</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>44957</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45834,7 +45834,7 @@
         <v>44957</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45981</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>45188</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45628</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45637</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>45562</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46282,7 +46282,7 @@
         <v>46029</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>45572</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45544</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>46041</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>44900</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>46042</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>44725</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>45260</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46876,7 +46876,7 @@
         <v>46044</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>44515</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>45252</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>46043</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>44630</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45337</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45194</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45147</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>46140</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>46048</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45453</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47679,7 +47679,7 @@
         <v>45985</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>46048</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45834</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>45299</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45775</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>46141</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>44865</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>46141</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>46056</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>46141</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48409,7 +48409,7 @@
         <v>46057</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>46057</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45911</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>46059</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>46141</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>45576</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>46142</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>46141</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>46141</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>46139</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49144,7 +49144,7 @@
         <v>46051</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>46063</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>46141</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49368,7 +49368,7 @@
         <v>46064</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>46146</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49514,7 +49514,7 @@
         <v>46148</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>46148</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>46065</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>46148</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49821,7 +49821,7 @@
         <v>46148</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>46066</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>46147</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>46147</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>46072</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>46101</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45147</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>45254</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50430,7 +50430,7 @@
         <v>46076</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>46153</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>46080</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>46084</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>46085</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>46085</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>46155</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>46160</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>46091</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>46160</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51175,7 +51175,7 @@
         <v>46090</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>46091</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>46160</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>46161</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51472,7 +51472,7 @@
         <v>46162</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>46161</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>46163</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>46164</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>46163</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45981</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>46094</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51993,7 +51993,7 @@
         <v>46168</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>46168</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>46170</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>46170</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>46170</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>46174</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>46163</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>46098</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>46182</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>46148</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>46184</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52816,7 +52816,7 @@
         <v>46185</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>46188</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52967,7 +52967,7 @@
         <v>46191</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>46191</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>46191</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53196,7 +53196,7 @@
         <v>46190</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53274,7 +53274,7 @@
         <v>46191</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53352,7 +53352,7 @@
         <v>46191</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>46191</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53508,7 +53508,7 @@
         <v>46190</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>46191</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53664,7 +53664,7 @@
         <v>46195</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>46196</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53810,7 +53810,7 @@
         <v>46197</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>46197</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53966,7 +53966,7 @@
         <v>46197</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54044,7 +54044,7 @@
         <v>46201</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>46202</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>46202</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54263,7 +54263,7 @@
         <v>46205</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54336,7 +54336,7 @@
         <v>46205</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>46211</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>46266</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>46220</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>46266</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54701,7 +54701,7 @@
         <v>46268</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>46274</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54847,7 +54847,7 @@
         <v>46266</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>46237</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>46237</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>46233</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55144,7 +55144,7 @@
         <v>46279</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>46239</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>46282</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55368,7 +55368,7 @@
         <v>46282</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55446,7 +55446,7 @@
         <v>46282</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>46286</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>46286</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>46286</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>46286</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>46287</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>46287</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55982,7 +55982,7 @@
         <v>46288</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56055,7 +56055,7 @@
         <v>46287</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56128,7 +56128,7 @@
         <v>46245</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56201,7 +56201,7 @@
         <v>46244</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>46184</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>46287</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56425,7 +56425,7 @@
         <v>46287</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56498,7 +56498,7 @@
         <v>46245</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>46246</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>46246</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>46105</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>46290</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>46248</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>46293</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>46248</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>46295</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>46297</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57243,7 +57243,7 @@
         <v>46258</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>46301</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57394,7 +57394,7 @@
         <v>46303</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57467,7 +57467,7 @@
         <v>46303</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>46260</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57613,7 +57613,7 @@
         <v>46304</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45999</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>46303</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>45728</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57910,7 +57910,7 @@
         <v>44550</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>44602</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58066,7 +58066,7 @@
         <v>45341</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58139,7 +58139,7 @@
         <v>45315</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>44893</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>44522</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58373,7 +58373,7 @@
         <v>45258</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45616</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>45881</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58602,7 +58602,7 @@
         <v>45915</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>45679</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>46021</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>46035</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58904,7 +58904,7 @@
         <v>46035</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         <v>46043</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>46125</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -601,7 +601,7 @@
         <v>45763</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45118</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>45737</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>45775</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>46037</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>46303</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45826</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>45853</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45932</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45666</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45826</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46071</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45967</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>46201</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45919</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>46287</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>46246</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>46248</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>45959</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45590</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>46230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>45625</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>46147</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>45992</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45217</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>46281</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>45792</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46281</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>46303</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>45848</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>46177</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>45978</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45833</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>45653</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>45533</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>46167</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>45003</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45925</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45895</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>45981</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45902</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>46112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>46206</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>46036</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>45264</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>46006</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>45841</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>46089</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>46178</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45525</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>46303</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44942</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>46260</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>46276</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>45623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>46112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>46078</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>46248</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>45982</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45848</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>44725</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44637</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>46008</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>46297</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>46105</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>45985</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>46002</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>45833</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>44796</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45890</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>46202</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>46202</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>46206</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45418</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>46237</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46085</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45835</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>46248</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>46248</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45848</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45481</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45782</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>44545</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>45967</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45966</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>46008</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45791</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45320</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>44881</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44742</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>46162</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>46198</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45533</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45852</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>46303</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>45775</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45007</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45090</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>45159</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45180</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45756</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45219</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>44589</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>44953</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45098</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45077</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45540</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46006</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>46237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>46029</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>44959</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45471</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>45826</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>44893</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>46301</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44945</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>46311</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44897</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44529</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45618</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45576</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45264</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45377</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>46089</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44553</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>44546</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>44813</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>44515</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44832</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>44838</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44601</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>44705</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>44516</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>44747</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>44848</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44844</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44673</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44788</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>44523</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>44609</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>44578</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44546</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44530</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44749</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>44589</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44543</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44680</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44858</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44796</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44810</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44522</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44613</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44656</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44726</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45036</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45894</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>45891</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45800</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45551</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45334</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45891</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45896</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45799</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45897</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45898</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44581</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45902</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45901</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44956</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45902</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45904</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45755</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>44909</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>46160</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>45590</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>46161</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45622</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45911</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45912</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>46162</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>46161</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44953</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>44953</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44957</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>44957</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>46163</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>45916</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46164</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>46163</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45981</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45919</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45637</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>46094</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>46168</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45572</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45924</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>44900</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45412</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>44725</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>46168</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>44515</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>45925</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45222</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>44630</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45337</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45194</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45929</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>46170</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>46170</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45930</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>45929</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>44847</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45147</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>45931</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45453</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>46170</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45931</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45931</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45938</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45937</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45415</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45299</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45938</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45937</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>44865</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>46174</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>44838</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45460</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45253</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45420</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>46163</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45210</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45425</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>45001</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45642</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>45615</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>46098</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45952</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45761</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44644</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>46182</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45196</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44937</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>46148</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45775</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45769</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>46184</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>46185</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45958</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45958</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45960</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45960</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45771</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45960</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45960</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45960</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45960</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>46188</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>45351</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>45961</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>45363</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26566,7 +26566,7 @@
         <v>45965</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45448</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45965</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>46191</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>46191</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>46191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>46190</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>46191</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>46191</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>45968</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>46191</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>46190</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>45967</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45967</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>45966</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>46195</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>46196</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45279</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45440</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>46197</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>45072</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>46197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>46197</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>46201</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45615</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45977</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45979</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46202</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45980</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45568</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45979</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>46202</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44497</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>45982</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>45981</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>45259</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45296</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>46205</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>46205</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45497</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45988</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45632</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45756</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>46211</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45749</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45992</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45992</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>45743</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45194</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45968</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>45992</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45695</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45433</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45748</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>45999</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45239</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>45278</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45593</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45463</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>45205</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>46001</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>46001</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>46220</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>46002</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>46002</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>46002</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>46006</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>46003</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>46006</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45784</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>46008</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>46008</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>46007</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>46008</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>44852</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>46009</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>45807</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32247,7 +32247,7 @@
         <v>45408</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45807</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>46009</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>46014</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>46237</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>46014</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>46013</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>46237</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>45954</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>46233</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>46013</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>46279</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>46239</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>46282</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>45725</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>46024</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>46282</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45625</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45625</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>45232</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45638</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45785</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45625</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>46286</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>46286</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>44720</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>44796</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45715</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>46286</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>46286</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>46029</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>46287</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>46287</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>46288</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>45272</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34925,7 +34925,7 @@
         <v>46041</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34998,7 +34998,7 @@
         <v>45049</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35071,7 +35071,7 @@
         <v>46287</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35144,7 +35144,7 @@
         <v>46042</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>45791</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>46245</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>46244</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>46044</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>46043</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45798</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>46184</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>46287</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         <v>46287</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45797</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>45798</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>46245</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36108,7 +36108,7 @@
         <v>46246</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>46246</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>46105</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>45524</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>46290</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>45810</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>46056</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>45625</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45497</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>46057</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>45439</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>46057</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>45911</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>45810</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>46059</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45810</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>45742</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>46248</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45705</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>45812</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>46063</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>46064</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45813</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>46065</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>46066</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46293</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46248</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45820</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>46072</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45820</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45820</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>45821</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>46076</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45826</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>45826</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>46295</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45825</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>46080</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45831</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>44874</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45831</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>45831</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>46084</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46297</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45831</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>46085</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>46085</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>46091</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>46090</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>46091</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45174</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>46052</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>46098</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45846</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>44531</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>46258</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>46301</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>45855</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>45358</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40460,7 +40460,7 @@
         <v>46112</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>44819</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>45866</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>46121</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>46119</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>46122</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>46260</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>46304</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>46127</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>45072</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45999</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>46303</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41341,7 +41341,7 @@
         <v>46127</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41414,7 +41414,7 @@
         <v>45874</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>46126</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         <v>45876</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45499</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45881</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>44898</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>44911</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45614</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>46133</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45645</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>46105</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>46134</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>45460</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42368,7 +42368,7 @@
         <v>46106</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>45820</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45567</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45646</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45624</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>46119</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>46135</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>46266</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>46266</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45812</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>46309</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43186,7 +43186,7 @@
         <v>44658</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>46266</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45810</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>44517</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45617</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>45667</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43624,7 +43624,7 @@
         <v>45551</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>45385</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>46310</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>46062</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44845</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>45981</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>46268</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>45188</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45628</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>45562</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>45544</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45240</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45260</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44573,7 +44573,7 @@
         <v>46191</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44651,7 +44651,7 @@
         <v>45252</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>46140</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44797,7 +44797,7 @@
         <v>46048</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>45985</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>46048</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45834</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>46274</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>45775</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>46141</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>44995</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>45404</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45454,7 +45454,7 @@
         <v>45573</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>46141</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>46141</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45576</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45751,7 +45751,7 @@
         <v>46141</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45576</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>44694</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>46142</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45691</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45229</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>46141</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>46141</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44907</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>46139</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>44897</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>45554</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>46051</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>46141</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45203</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46856,7 +46856,7 @@
         <v>46146</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46929,7 +46929,7 @@
         <v>45057</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
         <v>46148</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>46148</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45574</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>46148</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>46148</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45184</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>46147</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>46147</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>45615</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46101</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45147</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45254</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>46153</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>45279</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>46155</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48152,7 +48152,7 @@
         <v>46160</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48225,7 +48225,7 @@
         <v>46160</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>44831</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>45019</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48449,7 +48449,7 @@
         <v>45090</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45602</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>45145</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>45631</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>45474</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44642</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48887,7 +48887,7 @@
         <v>45645</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>45632</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45184</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49111,7 +49111,7 @@
         <v>44768</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>45756</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>44810</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>44959</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45530</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45502</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>45572</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49637,7 +49637,7 @@
         <v>45063</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>44851</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>44533</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>45173</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>44518</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
         <v>45524</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45476</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
         <v>45476</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50226,7 +50226,7 @@
         <v>45077</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45334</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45232</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>44806</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45264</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>45264</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>44837</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>45252</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50825,7 +50825,7 @@
         <v>45632</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45253</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50971,7 +50971,7 @@
         <v>45299</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45280</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45757</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>44903</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         <v>45105</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45296</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51409,7 +51409,7 @@
         <v>45520</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51482,7 +51482,7 @@
         <v>44915</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51555,7 +51555,7 @@
         <v>45259</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45761</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45463</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>45264</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>44896</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>45756</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45343</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>45387</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>45561</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>45259</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45132</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>45105</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52441,7 +52441,7 @@
         <v>44600</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         <v>45279</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45159</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>45505</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>45544</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>44957</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>45104</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45567</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>44589</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45692</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>45771</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45761</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53327,7 +53327,7 @@
         <v>45410</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53400,7 +53400,7 @@
         <v>45611</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>44581</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45210</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         <v>45572</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>45551</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>45628</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45351</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>45502</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45188</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>45420</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>45196</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>44830</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45695</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>44617</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>45607</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54495,7 +54495,7 @@
         <v>45162</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45754</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>44859</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>45215</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54787,7 +54787,7 @@
         <v>44699</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54860,7 +54860,7 @@
         <v>45761</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>45761</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>45090</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55089,7 +55089,7 @@
         <v>45775</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>45153</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45531</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55308,7 +55308,7 @@
         <v>45404</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55381,7 +55381,7 @@
         <v>45198</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55454,7 +55454,7 @@
         <v>45188</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55527,7 +55527,7 @@
         <v>44781</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55600,7 +55600,7 @@
         <v>45203</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55673,7 +55673,7 @@
         <v>45232</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55746,7 +55746,7 @@
         <v>45190</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45756</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55897,7 +55897,7 @@
         <v>45756</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>45247</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45245</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45272</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>44838</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>44755</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>44804</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>45162</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>45477</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>44859</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45259</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>44900</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56778,7 +56778,7 @@
         <v>45520</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56851,7 +56851,7 @@
         <v>45567</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>45167</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56997,7 +56997,7 @@
         <v>45229</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>45008</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>44887</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57221,7 +57221,7 @@
         <v>45188</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45376</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57367,7 +57367,7 @@
         <v>45728</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>44550</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57523,7 +57523,7 @@
         <v>44602</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>45341</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57674,7 +57674,7 @@
         <v>45315</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57752,7 +57752,7 @@
         <v>44893</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>44522</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57908,7 +57908,7 @@
         <v>45258</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57981,7 +57981,7 @@
         <v>45616</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58059,7 +58059,7 @@
         <v>45881</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58137,7 +58137,7 @@
         <v>45915</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58215,7 +58215,7 @@
         <v>45679</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58288,7 +58288,7 @@
         <v>46021</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58361,7 +58361,7 @@
         <v>46035</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>46035</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58517,7 +58517,7 @@
         <v>46043</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>46125</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
